--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487706_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487706_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0524</v>
+        <v>7.7953</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5485</v>
+        <v>6.2097</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5039</v>
+        <v>1.5856</v>
       </c>
       <c r="G2" t="n">
         <v>3.6142</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1263</v>
+        <v>0.8692</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6662</v>
+        <v>-0.0051</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7925</v>
+        <v>0.8743</v>
       </c>
       <c r="V2" t="n">
         <v>2.7298</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.417</v>
+        <v>5.8413</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4642</v>
+        <v>5.725</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0472</v>
+        <v>0.1163</v>
       </c>
       <c r="G3" t="n">
         <v>1.3714</v>
@@ -688,13 +688,13 @@
         <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5576</v>
+        <v>0.9819</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0595</v>
+        <v>0.2013</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6171</v>
+        <v>0.7806</v>
       </c>
       <c r="V3" t="n">
         <v>3.294</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6358</v>
+        <v>4.3156</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7589</v>
+        <v>2.3901</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1232</v>
+        <v>1.9255</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7437</v>
+        <v>3.6308</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8766</v>
+        <v>0.8074</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1329</v>
+        <v>2.8235</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1694</v>
+        <v>4.6506</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3347</v>
+        <v>0.8651</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8348</v>
+        <v>3.7856</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4258</v>
+        <v>-1.0198</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4581</v>
+        <v>-0.0577</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9677</v>
+        <v>-0.9621</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>-2.1344</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>2.116</v>
+        <v>0.4907</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3358</v>
+        <v>-0.1262</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7802</v>
+        <v>0.6169</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3273</v>
+        <v>2.7443</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7289</v>
+        <v>3.0582</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5984</v>
+        <v>-0.3139</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6308</v>
+        <v>0.7437</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8074</v>
+        <v>0.8766</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8235</v>
+        <v>-0.1329</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6506</v>
+        <v>2.1694</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8651</v>
+        <v>1.3347</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7856</v>
+        <v>0.8348</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0198</v>
+        <v>-1.4258</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0577</v>
+        <v>-0.4581</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9621</v>
+        <v>-0.9677</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3284</v>
+        <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4975</v>
+        <v>1.2245</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7874</v>
+        <v>0.6351</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2898</v>
+        <v>0.5894</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0264</v>
+        <v>1.3229</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3001</v>
+        <v>1.76</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2736</v>
+        <v>-0.4372</v>
       </c>
       <c r="G6" t="n">
         <v>0.2661</v>
@@ -922,13 +922,13 @@
         <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7707</v>
+        <v>1.0672</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6684</v>
+        <v>0.1284</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1023</v>
+        <v>0.9388</v>
       </c>
       <c r="V6" t="n">
         <v>0.3776</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8879</v>
+        <v>0.6515</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6251</v>
+        <v>0.525</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2628</v>
+        <v>0.1265</v>
       </c>
       <c r="G7" t="n">
         <v>0.1109</v>
@@ -1000,13 +1000,13 @@
         <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6606</v>
+        <v>0.4242</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1828</v>
+        <v>0.0827</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4778</v>
+        <v>0.3415</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6597</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4902</v>
+        <v>-0.7169</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5828</v>
+        <v>-0.3773</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.073</v>
+        <v>-0.3396</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6396</v>
+        <v>-2.7293</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5429</v>
+        <v>-1.2556</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0966</v>
+        <v>-1.4737</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4307</v>
+        <v>-0.8537</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0504</v>
+        <v>-0.8815</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3803</v>
+        <v>0.0279</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7912</v>
+        <v>-1.8756</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5075</v>
+        <v>-0.374</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2836</v>
+        <v>-1.5015</v>
       </c>
       <c r="P8" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>0.406</v>
+        <v>-0.0757</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1222</v>
+        <v>-0.0595</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2838</v>
+        <v>-0.0162</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7298</v>
+        <v>1.506</v>
       </c>
       <c r="W8" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-2.7298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7442</v>
+        <v>-1.0269</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3773</v>
+        <v>1.1824</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3668</v>
+        <v>-2.2093</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.7293</v>
+        <v>1.6396</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2556</v>
+        <v>0.5429</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4737</v>
+        <v>1.0966</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8537</v>
+        <v>2.4307</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8815</v>
+        <v>1.0504</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0279</v>
+        <v>1.3803</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8756</v>
+        <v>-0.7912</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.374</v>
+        <v>-0.5075</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5015</v>
+        <v>-0.2836</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.103</v>
+        <v>-0.1307</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0595</v>
+        <v>-0.2782</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0435</v>
+        <v>0.1475</v>
       </c>
       <c r="V9" t="n">
-        <v>1.506</v>
+        <v>-2.7298</v>
       </c>
       <c r="W9" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9058</v>
+        <v>-1.0816</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4644</v>
+        <v>-0.504</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4414</v>
+        <v>-0.5777</v>
       </c>
       <c r="G10" t="n">
         <v>-0.83</v>
@@ -1234,13 +1234,13 @@
         <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6913</v>
+        <v>1.5155</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6079</v>
+        <v>0.5683</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0835</v>
+        <v>0.9472</v>
       </c>
       <c r="V10" t="n">
         <v>-2.5433</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9456</v>
+        <v>-2.2815</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0644</v>
+        <v>0.4361</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8812</v>
+        <v>-2.7176</v>
       </c>
       <c r="G11" t="n">
         <v>1.3358</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7277</v>
+        <v>-0.0636</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6662</v>
+        <v>-0.1657</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0614</v>
+        <v>0.1021</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7776</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.261</v>
+        <v>17.564</v>
       </c>
       <c r="E12" t="n">
-        <v>20.1024</v>
+        <v>20.4052</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8413</v>
+        <v>-2.8414</v>
       </c>
       <c r="G12" t="n">
         <v>9.1532</v>
@@ -1390,13 +1390,13 @@
         <v>16.4928</v>
       </c>
       <c r="S12" t="n">
-        <v>6.000299999999999</v>
+        <v>6.3032</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6783</v>
+        <v>0.9811000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>5.3221</v>
+        <v>5.322100000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8030000000000008</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7625</v>
+        <v>3.8893</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5663</v>
+        <v>4.3661</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.4768</v>
       </c>
       <c r="G13" t="n">
         <v>4.058</v>
@@ -1468,13 +1468,13 @@
         <v>0.9702</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.8182</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2894</v>
+        <v>-0.4896</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.3286</v>
       </c>
       <c r="V13" t="n">
         <v>1.6197</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0791</v>
+        <v>1.3511</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5071</v>
+        <v>1.8064</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.428</v>
+        <v>-0.4553</v>
       </c>
       <c r="G14" t="n">
         <v>0.8126</v>
@@ -1546,13 +1546,13 @@
         <v>0.9702</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7826</v>
+        <v>0.0547</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5596</v>
+        <v>-0.1411</v>
       </c>
       <c r="U14" t="n">
-        <v>0.223</v>
+        <v>0.1957</v>
       </c>
       <c r="V14" t="n">
         <v>0.6778999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4726</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7539</v>
+        <v>3.4536</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2813</v>
+        <v>-2.5538</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1261</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1211</v>
+        <v>-0.4517</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0348</v>
+        <v>-0.3351</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1559</v>
+        <v>-0.1166</v>
       </c>
       <c r="V15" t="n">
         <v>3.0597</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8531</v>
+        <v>-0.7168</v>
       </c>
       <c r="E16" t="n">
         <v>-0.3139</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5392</v>
+        <v>-0.4029</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6342</v>
@@ -1702,13 +1702,13 @@
         <v>0.194</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2849</v>
+        <v>-0.1486</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0426</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.066</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1932</v>
+        <v>-0.8022</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4651</v>
+        <v>-0.2649</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7281</v>
+        <v>-0.5373</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8918</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6673</v>
+        <v>-1.2763</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3325</v>
+        <v>-1.1323</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3349</v>
+        <v>-0.1441</v>
       </c>
       <c r="V17" t="n">
         <v>1.0078</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>F. QUERO CARMONA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1247</v>
+        <v>-1.9734</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4946</v>
+        <v>-0.8202</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6301</v>
+        <v>-1.1533</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9566</v>
+        <v>-0.9306</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2959</v>
+        <v>-0.4029</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6607</v>
+        <v>-0.5278</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1105</v>
+        <v>0.4553</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2729</v>
+        <v>0.4325</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1624</v>
+        <v>0.0228</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8462</v>
+        <v>-1.386</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0231</v>
+        <v>-0.8354</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.5506</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="R18" t="n">
         <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3401</v>
+        <v>0.1035</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4722</v>
+        <v>-0.1113</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1321</v>
+        <v>0.2148</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2161</v>
+        <v>-0.5642</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4982</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. QUERO CARMONA</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.301</v>
+        <v>-2.0881</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1205</v>
+        <v>-1.2944</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1805</v>
+        <v>-0.7936</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9306</v>
+        <v>-1.9566</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4029</v>
+        <v>-1.2959</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5278</v>
+        <v>-0.6607</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4553</v>
+        <v>-1.1105</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4325</v>
+        <v>-1.2729</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0228</v>
+        <v>0.1624</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.386</v>
+        <v>-0.8462</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8354</v>
+        <v>-0.0231</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5506</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="R19" t="n">
         <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2241</v>
+        <v>-0.3034</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4116</v>
+        <v>-0.272</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1875</v>
+        <v>-0.0314</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5642</v>
+        <v>-0.2161</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5642</v>
+        <v>-0.4982</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8927</v>
+        <v>-2.6108</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4079</v>
+        <v>0.6081</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3006</v>
+        <v>-3.2189</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2857</v>
@@ -2014,13 +2014,13 @@
         <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8786</v>
+        <v>-0.5967</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8962</v>
+        <v>-0.696</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0175</v>
+        <v>0.0993</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5642</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3811</v>
+        <v>-2.9079</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3334</v>
+        <v>0.1671</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0477</v>
+        <v>-3.0749</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4004</v>
@@ -2092,13 +2092,13 @@
         <v>2.3284</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2912</v>
+        <v>-0.8179</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.005</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2862</v>
+        <v>-0.3135</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6597</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6772</v>
+        <v>-5.1866</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.237</v>
+        <v>-3.6374</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4402</v>
+        <v>-1.5492</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0044</v>
@@ -2170,13 +2170,13 @@
         <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3026</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3623</v>
+        <v>-0.7627</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0597</v>
+        <v>-0.0493</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5642</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1522</v>
+        <v>-7.1156</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4294</v>
+        <v>-1.2292</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.7229</v>
+        <v>-5.8864</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7938</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9704</v>
+        <v>-0.9337</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8356</v>
+        <v>-0.6354</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1348</v>
+        <v>-0.2983</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0597</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.261</v>
+        <v>-17.2613</v>
       </c>
       <c r="E24" t="n">
-        <v>2.841299999999999</v>
+        <v>2.841300000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-20.1025</v>
+        <v>-20.1024</v>
       </c>
       <c r="G24" t="n">
         <v>-9.153</v>
@@ -2326,13 +2326,13 @@
         <v>13.5823</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.0006</v>
+        <v>-6.0003</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.3223</v>
+        <v>-5.322299999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6785</v>
+        <v>-0.6783</v>
       </c>
       <c r="V24" t="n">
         <v>0.802999999999999</v>
